--- a/docs/ValueSet-ahip-birth-sex.xlsx
+++ b/docs/ValueSet-ahip-birth-sex.xlsx
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on SNOMED CT and US Core Birth Sex Value Set</t>
+    <t>Used as the answer options for the birth sex question in the SOGI and Relationship Status Section, capturing the sex a patient was assigned at birth. Based on SNOMED CT and US Core Birth Sex Value Set</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -110,13 +110,13 @@
     <t>248153007</t>
   </si>
   <si>
-    <t>Male</t>
+    <t>Male, Man</t>
   </si>
   <si>
     <t>248152002</t>
   </si>
   <si>
-    <t>Female</t>
+    <t>Female, Woman</t>
   </si>
   <si>
     <t>32570691000036108</t>
@@ -137,7 +137,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
   <si>
     <t>ASKU</t>

--- a/docs/ValueSet-ahip-birth-sex.xlsx
+++ b/docs/ValueSet-ahip-birth-sex.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -95,7 +94,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -110,13 +111,13 @@
     <t>248153007</t>
   </si>
   <si>
-    <t>Male, Man</t>
+    <t>Male</t>
   </si>
   <si>
     <t>248152002</t>
   </si>
   <si>
-    <t>Female, Woman</t>
+    <t>Female</t>
   </si>
   <si>
     <t>32570691000036108</t>
@@ -129,15 +130,6 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>CNTR</t>
-  </si>
-  <si>
-    <t>I choose not to respond at this time</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
   <si>
     <t>ASKU</t>
@@ -516,50 +508,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>